--- a/outputs/evaluation/architecture/design/v2/CF_M05/run_1/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v2/CF_M05/run_1/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.3171</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.3529</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9242</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.1429</v>
       </c>
       <c r="D4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.7829</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7829</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_02', 'AU_03']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_09</t>
@@ -1233,7 +1245,6 @@
           <t>portal, access control</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M05_AU14, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU34</t>
@@ -1303,14 +1313,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1337,13 +1344,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1384,14 +1389,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1417,13 +1419,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1464,14 +1464,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1500,13 +1497,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1547,14 +1542,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1583,13 +1575,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1630,14 +1620,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1662,13 +1649,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1714,13 +1699,11 @@
           <t>['AU_07']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -1742,14 +1725,11 @@
       <c r="P8" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1790,14 +1770,11 @@
           <t>80</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
@@ -1823,13 +1800,11 @@
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1875,13 +1850,11 @@
           <t>['AU_01', 'AU_03', 'AU_04', 'AU_05']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -1907,13 +1880,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1959,13 +1930,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -1985,14 +1954,11 @@
       <c r="P11" t="n">
         <v>62</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2038,13 +2004,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -2068,13 +2032,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2115,14 +2077,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -2141,14 +2100,11 @@
       <c r="P13" t="n">
         <v>56</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2189,14 +2145,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -2217,7 +2170,6 @@
       <c r="P14" t="n">
         <v>61</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -2228,7 +2180,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2315,7 +2266,6 @@
           <t>Client(Frontend)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The client, also called the frontEnd, is responsible for the presentation and user experience
@@ -2353,7 +2303,6 @@
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>SonarQube is a
@@ -2392,7 +2341,6 @@
           <t>Grafana</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
@@ -2428,7 +2376,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -2465,7 +2412,6 @@
           <t>Ordering</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -2502,7 +2448,6 @@
           <t>GSB</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -2539,7 +2484,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
@@ -2577,7 +2521,6 @@
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
@@ -2615,7 +2558,6 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
@@ -2653,7 +2595,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -2691,7 +2632,6 @@
           <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>The controllers, through specific
@@ -2729,7 +2669,6 @@
           <t>Business Logic Layer (Services)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Services provide the interface and implementation of all the application's business logic.</t>
@@ -2765,7 +2704,6 @@
           <t>Domain Layer (Models)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Models represent the internal and persistent structure of the system entities, reflecting the
@@ -2802,7 +2740,6 @@
           <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
@@ -2839,7 +2776,6 @@
           <t>Data access layer (Repositories)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>the Repositories are responsible for performing queries on the database.</t>
@@ -2870,7 +2806,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
@@ -2906,7 +2841,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client(frontend), amazon eks</t>
@@ -2942,7 +2876,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>client(frontend), server (backend)</t>
@@ -2978,7 +2911,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -2994,7 +2926,6 @@
           <t>AU_09</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0.7049</v>
       </c>
@@ -3010,7 +2941,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>data access layer (repositories), database</t>
@@ -3026,7 +2956,6 @@
           <t>AU_09</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>0.6458</v>
       </c>
@@ -3042,7 +2971,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -3083,7 +3011,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -3120,7 +3047,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>The message
@@ -3132,7 +3058,6 @@
           <t>AU_09</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>0.9088000000000001</v>
       </c>
@@ -3153,7 +3078,6 @@
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
@@ -3190,7 +3114,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
@@ -3226,7 +3149,6 @@
           <t>Kubernetes</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>which allows the use of Kubernetes (K8s), a container orchestration platform created by
@@ -3263,7 +3185,6 @@
           <t>Cloud Architecture</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
@@ -3300,7 +3221,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
